--- a/data/trans_dic/IP07_C14_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C14_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 28,33</t>
+          <t>5,14; 27,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 27,01</t>
+          <t>7,39; 29,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,09; 24,49</t>
+          <t>7,78; 23,36</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 18,31</t>
+          <t>5,13; 29,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,81; 32,09</t>
+          <t>1,9; 16,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,07; 20,57</t>
+          <t>5,52; 19,45</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,1</t>
+          <t>2,04; 25,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 26,74</t>
+          <t>0,0; 21,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 21,27</t>
+          <t>3,4; 19,85</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 28,07</t>
+          <t>6,42; 24,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,84; 24,43</t>
+          <t>13,32; 36,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,41; 20,82</t>
+          <t>10,79; 24,53</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 26,69</t>
+          <t>4,06; 22,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 22,21</t>
+          <t>6,51; 25,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 19,67</t>
+          <t>6,64; 19,03</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,77; 30,68</t>
+          <t>4,17; 25,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,23; 25,6</t>
+          <t>5,23; 28,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,37; 22,19</t>
+          <t>6,91; 20,97</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,61; 17,68</t>
+          <t>8,48; 16,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,51; 17,7</t>
+          <t>10,53; 19,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,8; 15,98</t>
+          <t>10,36; 16,13</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9354</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1778; 8296</t>
+          <t>1777; 9357</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2114; 9096</t>
+          <t>2266; 9148</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5725; 15418</t>
+          <t>5077; 15252</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>6824</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>622; 5220</t>
+          <t>1577; 9207</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2040; 9622</t>
+          <t>573; 4857</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3553; 12028</t>
+          <t>3358; 11839</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3487</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3547</t>
+          <t>538; 6842</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>522; 7222</t>
+          <t>0; 3316</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1366; 8749</t>
+          <t>1414; 8249</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18151</t>
+          <t>17774</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2159; 18446</t>
+          <t>4047; 15616</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4427; 15806</t>
+          <t>5614; 15440</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8354; 27149</t>
+          <t>11354; 25805</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>10882</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1972; 8738</t>
+          <t>2326; 12764</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2498; 13105</t>
+          <t>2325; 9064</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5422; 18049</t>
+          <t>6181; 17700</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8173</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1920; 8698</t>
+          <t>1376; 8433</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1698; 8318</t>
+          <t>1630; 8868</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4485; 13505</t>
+          <t>4433; 13450</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>25810</t>
+          <t>29969</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>31710</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57520</t>
+          <t>56493</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15131; 35122</t>
+          <t>20790; 39963</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23480; 43695</t>
+          <t>19477; 35312</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43686; 71182</t>
+          <t>44556; 69377</t>
         </is>
       </c>
     </row>
